--- a/Raw_Data/v7a_2040_yoll_Europe.xlsx
+++ b/Raw_Data/v7a_2040_yoll_Europe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF98256-CB15-4E3B-BBDD-EA7917D2EDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2873D7D7-328E-4B1F-8409-8FC26B31F562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-2730" windowWidth="19410" windowHeight="20985" xr2:uid="{0FF85C77-6106-4259-AF19-728A5860A454}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FF85C77-6106-4259-AF19-728A5860A454}"/>
   </bookViews>
   <sheets>
     <sheet name="yoll_Europe (13)" sheetId="12" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="yoll_Europe (5)" sheetId="4" r:id="rId9"/>
     <sheet name="yoll_Europe (4)" sheetId="2" r:id="rId10"/>
     <sheet name="yoll_Europe (3)" sheetId="3" r:id="rId11"/>
-    <sheet name="yoll_Europe (2)" sheetId="1" r:id="rId12"/>
+    <sheet name="yoll_Europe" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,9 +47,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="77">
   <si>
     <t>Premature mortality due to PM2.5</t>
-  </si>
-  <si>
-    <t>Scenario: LRTAP_Baseline_v7</t>
   </si>
   <si>
     <t xml:space="preserve">Region: </t>
@@ -275,6 +272,9 @@
   </si>
   <si>
     <t>Scenario: OPT Health -60 AAE -50 v7a</t>
+  </si>
+  <si>
+    <t>Scenario: Baseline_v7a</t>
   </si>
 </sst>
 </file>
@@ -1145,55 +1145,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -1216,10 +1216,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -1268,10 +1268,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -1736,10 +1736,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -1788,10 +1788,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -1840,10 +1840,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -1993,10 +1993,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -2071,10 +2071,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -2253,10 +2253,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -2279,10 +2279,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -2383,10 +2383,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -2551,55 +2551,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -2648,10 +2648,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -2700,10 +2700,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -2752,10 +2752,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -2856,10 +2856,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -2882,10 +2882,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -2908,10 +2908,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -2960,10 +2960,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -3142,10 +3142,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -3194,10 +3194,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -3220,10 +3220,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -3246,10 +3246,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -3272,10 +3272,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -3298,7 +3298,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -3321,10 +3321,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -3347,10 +3347,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -3451,10 +3451,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -3555,10 +3555,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -3633,10 +3633,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -3685,10 +3685,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -3763,10 +3763,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -3841,10 +3841,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -3867,10 +3867,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -3957,55 +3957,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -4028,10 +4028,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -4054,10 +4054,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -4132,10 +4132,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -4210,10 +4210,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -4262,10 +4262,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -4314,10 +4314,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -4340,10 +4340,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -4418,10 +4418,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -4444,10 +4444,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -4522,10 +4522,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -4548,10 +4548,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -4574,10 +4574,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -4626,10 +4626,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -4652,10 +4652,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -4678,10 +4678,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -4704,7 +4704,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -4727,10 +4727,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -4753,10 +4753,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -4831,10 +4831,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -4909,10 +4909,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -4935,10 +4935,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -5013,10 +5013,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -5039,10 +5039,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -5117,10 +5117,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -5143,10 +5143,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -5221,10 +5221,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -5247,10 +5247,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -5273,10 +5273,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -5325,7 +5325,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -5352,7 +5352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78C7EC19-BAEB-40DB-B188-6ED2FF19C722}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231A728B-B86D-46F2-B241-D89DAD486E32}">
   <dimension ref="A2:H61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -5363,171 +5363,171 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
       </c>
       <c r="D10">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="E10">
-        <v>39293</v>
+        <v>39166</v>
       </c>
       <c r="F10">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="G10">
-        <v>3210</v>
+        <v>3199</v>
       </c>
       <c r="H10">
-        <v>3968</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
       </c>
       <c r="D11">
-        <v>5.37</v>
+        <v>5.34</v>
       </c>
       <c r="E11">
-        <v>62822</v>
+        <v>62442</v>
       </c>
       <c r="F11">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="G11">
-        <v>5310</v>
+        <v>5277</v>
       </c>
       <c r="H11">
-        <v>6242</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
       </c>
       <c r="D12">
-        <v>5.84</v>
+        <v>5.83</v>
       </c>
       <c r="E12">
-        <v>51338</v>
+        <v>51282</v>
       </c>
       <c r="F12">
-        <v>5.6</v>
+        <v>5.59</v>
       </c>
       <c r="G12">
-        <v>5724</v>
+        <v>5718</v>
       </c>
       <c r="H12">
-        <v>5064</v>
+        <v>5058</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
       </c>
       <c r="D13">
-        <v>4.6900000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="E13">
-        <v>21261</v>
+        <v>21197</v>
       </c>
       <c r="F13">
-        <v>4.5</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="G13">
-        <v>2254</v>
+        <v>2247</v>
       </c>
       <c r="H13">
-        <v>2212</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
       </c>
       <c r="D14">
-        <v>6.04</v>
+        <v>6.03</v>
       </c>
       <c r="E14">
-        <v>7253</v>
+        <v>7246</v>
       </c>
       <c r="F14">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="G14">
         <v>395</v>
@@ -5538,36 +5538,36 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
       </c>
       <c r="D15">
-        <v>4.88</v>
+        <v>4.87</v>
       </c>
       <c r="E15">
-        <v>56794</v>
+        <v>56656</v>
       </c>
       <c r="F15">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="G15">
-        <v>4842</v>
+        <v>4830</v>
       </c>
       <c r="H15">
-        <v>5824</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -5576,24 +5576,24 @@
         <v>3.47</v>
       </c>
       <c r="E16">
-        <v>20239</v>
+        <v>20198</v>
       </c>
       <c r="F16">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="G16">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="H16">
-        <v>2134</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -5616,10 +5616,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -5628,7 +5628,7 @@
         <v>2.48</v>
       </c>
       <c r="E18">
-        <v>14173</v>
+        <v>14172</v>
       </c>
       <c r="F18">
         <v>2.08</v>
@@ -5642,114 +5642,114 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="E19">
-        <v>270295</v>
+        <v>269312</v>
       </c>
       <c r="F19">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="G19">
-        <v>21001</v>
+        <v>20925</v>
       </c>
       <c r="H19">
-        <v>26613</v>
+        <v>26517</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
       </c>
       <c r="D20">
-        <v>4.32</v>
+        <v>4.29</v>
       </c>
       <c r="E20">
-        <v>386735</v>
+        <v>384949</v>
       </c>
       <c r="F20">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="G20">
-        <v>35972</v>
+        <v>35806</v>
       </c>
       <c r="H20">
-        <v>39938</v>
+        <v>39754</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
       </c>
       <c r="D21">
-        <v>6.74</v>
+        <v>6.73</v>
       </c>
       <c r="E21">
-        <v>74176</v>
+        <v>74059</v>
       </c>
       <c r="F21">
-        <v>5.75</v>
+        <v>5.74</v>
       </c>
       <c r="G21">
-        <v>7423</v>
+        <v>7411</v>
       </c>
       <c r="H21">
-        <v>7448</v>
+        <v>7436</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
       </c>
       <c r="D22">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="E22">
-        <v>72579</v>
+        <v>72438</v>
       </c>
       <c r="F22">
-        <v>5.88</v>
+        <v>5.87</v>
       </c>
       <c r="G22">
-        <v>6760</v>
+        <v>6747</v>
       </c>
       <c r="H22">
-        <v>6726</v>
+        <v>6713</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -5758,7 +5758,7 @@
         <v>2.06</v>
       </c>
       <c r="E23">
-        <v>9428</v>
+        <v>9422</v>
       </c>
       <c r="F23">
         <v>1.65</v>
@@ -5772,62 +5772,62 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
       </c>
       <c r="D24">
-        <v>6.92</v>
+        <v>6.88</v>
       </c>
       <c r="E24">
-        <v>402201</v>
+        <v>400464</v>
       </c>
       <c r="F24">
-        <v>5.56</v>
+        <v>5.53</v>
       </c>
       <c r="G24">
-        <v>40057</v>
+        <v>39884</v>
       </c>
       <c r="H24">
-        <v>44734</v>
+        <v>44541</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
       </c>
       <c r="D25">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="E25">
-        <v>9662</v>
+        <v>9657</v>
       </c>
       <c r="F25">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="G25">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H25">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -5836,36 +5836,36 @@
         <v>4.01</v>
       </c>
       <c r="E26">
-        <v>15469</v>
+        <v>15459</v>
       </c>
       <c r="F26">
         <v>4.1900000000000004</v>
       </c>
       <c r="G26">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H26">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
       </c>
       <c r="D27">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="E27">
-        <v>2530</v>
+        <v>2520</v>
       </c>
       <c r="F27">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="G27">
         <v>144</v>
@@ -5876,114 +5876,114 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
       </c>
       <c r="D28">
-        <v>6.97</v>
+        <v>6.95</v>
       </c>
       <c r="E28">
-        <v>3867</v>
+        <v>3856</v>
       </c>
       <c r="F28">
-        <v>6.07</v>
+        <v>6.05</v>
       </c>
       <c r="G28">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H28">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
       </c>
       <c r="D29">
-        <v>5.71</v>
+        <v>5.68</v>
       </c>
       <c r="E29">
-        <v>98326</v>
+        <v>97775</v>
       </c>
       <c r="F29">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="G29">
-        <v>7503</v>
+        <v>7461</v>
       </c>
       <c r="H29">
-        <v>10638</v>
+        <v>10579</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
       </c>
       <c r="D30">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="E30">
-        <v>225481</v>
+        <v>225126</v>
       </c>
       <c r="F30">
-        <v>4.74</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="G30">
-        <v>16197</v>
+        <v>16172</v>
       </c>
       <c r="H30">
-        <v>20255</v>
+        <v>20223</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
       </c>
       <c r="D31">
-        <v>4.3099999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="E31">
-        <v>48570</v>
+        <v>48483</v>
       </c>
       <c r="F31">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="G31">
-        <v>4109</v>
+        <v>4102</v>
       </c>
       <c r="H31">
-        <v>5050</v>
+        <v>5041</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -5992,102 +5992,102 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>166846</v>
+        <v>166743</v>
       </c>
       <c r="F32">
         <v>7.1</v>
       </c>
       <c r="G32">
-        <v>16701</v>
+        <v>16691</v>
       </c>
       <c r="H32">
-        <v>15960</v>
+        <v>15950</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
       </c>
       <c r="D33">
-        <v>4.72</v>
+        <v>4.71</v>
       </c>
       <c r="E33">
-        <v>30820</v>
+        <v>30760</v>
       </c>
       <c r="F33">
-        <v>4.6500000000000004</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="G33">
-        <v>2224</v>
+        <v>2220</v>
       </c>
       <c r="H33">
-        <v>2847</v>
+        <v>2841</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
       </c>
       <c r="D34">
-        <v>6.26</v>
+        <v>6.25</v>
       </c>
       <c r="E34">
-        <v>14643</v>
+        <v>14600</v>
       </c>
       <c r="F34">
-        <v>5.39</v>
+        <v>5.37</v>
       </c>
       <c r="G34">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="H34">
-        <v>1439</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
       </c>
       <c r="D35">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="E35">
-        <v>224250</v>
+        <v>223505</v>
       </c>
       <c r="F35">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="G35">
-        <v>17904</v>
+        <v>17845</v>
       </c>
       <c r="H35">
-        <v>22470</v>
+        <v>22395</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -6096,125 +6096,125 @@
         <v>2.58</v>
       </c>
       <c r="E36">
-        <v>23636</v>
+        <v>23606</v>
       </c>
       <c r="F36">
         <v>2</v>
       </c>
       <c r="G36">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="H36">
-        <v>2630</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
       </c>
       <c r="D37">
-        <v>4.96</v>
+        <v>4.9400000000000004</v>
       </c>
       <c r="E37">
-        <v>2357853</v>
+        <v>2350257</v>
       </c>
       <c r="F37">
-        <v>4.29</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="G37">
-        <v>207336</v>
+        <v>206666</v>
       </c>
       <c r="H37">
-        <v>238610</v>
+        <v>237826</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
       </c>
       <c r="D38">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
       <c r="E38">
-        <v>27637</v>
+        <v>27607</v>
       </c>
       <c r="F38">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
       <c r="G38">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="H38">
-        <v>2703</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
       </c>
       <c r="D39">
-        <v>21.13</v>
+        <v>21.19</v>
       </c>
       <c r="E39">
-        <v>69086</v>
+        <v>69285</v>
       </c>
       <c r="F39">
-        <v>22.68</v>
+        <v>22.74</v>
       </c>
       <c r="G39">
-        <v>5255</v>
+        <v>5271</v>
       </c>
       <c r="H39">
-        <v>6152</v>
+        <v>6170</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
       </c>
       <c r="D40">
-        <v>11.76</v>
+        <v>11.82</v>
       </c>
       <c r="E40">
-        <v>129456</v>
+        <v>130147</v>
       </c>
       <c r="F40">
-        <v>12.43</v>
+        <v>12.49</v>
       </c>
       <c r="G40">
-        <v>6171</v>
+        <v>6203</v>
       </c>
       <c r="H40">
-        <v>10711</v>
+        <v>10768</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -6223,76 +6223,76 @@
         <v>6.75</v>
       </c>
       <c r="E41">
-        <v>85134</v>
+        <v>85021</v>
       </c>
       <c r="F41">
         <v>7.38</v>
       </c>
       <c r="G41">
-        <v>7178</v>
+        <v>7168</v>
       </c>
       <c r="H41">
-        <v>7438</v>
+        <v>7428</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
       </c>
       <c r="D42">
-        <v>12.19</v>
+        <v>12.18</v>
       </c>
       <c r="E42">
-        <v>49878</v>
+        <v>49836</v>
       </c>
       <c r="F42">
-        <v>12.02</v>
+        <v>12.01</v>
       </c>
       <c r="G42">
-        <v>4555</v>
+        <v>4551</v>
       </c>
       <c r="H42">
-        <v>4755</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
       </c>
       <c r="D43">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
       <c r="E43">
-        <v>52976</v>
+        <v>52917</v>
       </c>
       <c r="F43">
-        <v>11.01</v>
+        <v>10.99</v>
       </c>
       <c r="G43">
-        <v>4579</v>
+        <v>4574</v>
       </c>
       <c r="H43">
-        <v>4542</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -6315,166 +6315,166 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
       </c>
       <c r="D45">
-        <v>21.08</v>
+        <v>20.63</v>
       </c>
       <c r="E45">
-        <v>476890</v>
+        <v>466739</v>
       </c>
       <c r="F45">
-        <v>23.27</v>
+        <v>22.78</v>
       </c>
       <c r="G45">
-        <v>23355</v>
+        <v>22858</v>
       </c>
       <c r="H45">
-        <v>35054</v>
+        <v>34308</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
       </c>
       <c r="D46">
-        <v>18.07</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="E46">
-        <v>24859</v>
+        <v>24849</v>
       </c>
       <c r="F46">
-        <v>16.95</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="G46">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H46">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
       </c>
       <c r="D47">
-        <v>14.74</v>
+        <v>14.86</v>
       </c>
       <c r="E47">
-        <v>106126</v>
+        <v>106939</v>
       </c>
       <c r="F47">
-        <v>15.77</v>
+        <v>15.89</v>
       </c>
       <c r="G47">
-        <v>5125</v>
+        <v>5165</v>
       </c>
       <c r="H47">
-        <v>7911</v>
+        <v>7972</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
       </c>
       <c r="D48">
-        <v>9.48</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="E48">
-        <v>19090</v>
+        <v>19076</v>
       </c>
       <c r="F48">
-        <v>8.89</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="G48">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="H48">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
       </c>
       <c r="D49">
-        <v>9.25</v>
+        <v>9.27</v>
       </c>
       <c r="E49">
-        <v>39407</v>
+        <v>39481</v>
       </c>
       <c r="F49">
-        <v>9.82</v>
+        <v>9.84</v>
       </c>
       <c r="G49">
-        <v>3464</v>
+        <v>3471</v>
       </c>
       <c r="H49">
-        <v>3473</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
       </c>
       <c r="D50">
-        <v>13.03</v>
+        <v>13.02</v>
       </c>
       <c r="E50">
-        <v>9384</v>
+        <v>9377</v>
       </c>
       <c r="F50">
-        <v>12.3</v>
+        <v>12.29</v>
       </c>
       <c r="G50">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H50">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -6483,154 +6483,154 @@
         <v>2.41</v>
       </c>
       <c r="E51">
-        <v>11679</v>
+        <v>11665</v>
       </c>
       <c r="F51">
         <v>1.88</v>
       </c>
       <c r="G51">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H51">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
       </c>
       <c r="D52">
-        <v>9.19</v>
+        <v>9.25</v>
       </c>
       <c r="E52">
-        <v>1515673</v>
+        <v>1525673</v>
       </c>
       <c r="F52">
-        <v>10.23</v>
+        <v>10.3</v>
       </c>
       <c r="G52">
-        <v>110506</v>
+        <v>111235</v>
       </c>
       <c r="H52">
-        <v>117966</v>
+        <v>118745</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
       </c>
       <c r="D53">
-        <v>10.36</v>
+        <v>10.35</v>
       </c>
       <c r="E53">
-        <v>91280</v>
+        <v>91202</v>
       </c>
       <c r="F53">
-        <v>10.119999999999999</v>
+        <v>10.11</v>
       </c>
       <c r="G53">
-        <v>9225</v>
+        <v>9217</v>
       </c>
       <c r="H53">
-        <v>8719</v>
+        <v>8711</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
       </c>
       <c r="D54">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="E54">
-        <v>37675</v>
+        <v>37455</v>
       </c>
       <c r="F54">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="G54">
-        <v>2872</v>
+        <v>2856</v>
       </c>
       <c r="H54">
-        <v>3985</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
       </c>
       <c r="D55">
-        <v>18.2</v>
+        <v>18.28</v>
       </c>
       <c r="E55">
-        <v>155821</v>
+        <v>156542</v>
       </c>
       <c r="F55">
-        <v>20.23</v>
+        <v>20.32</v>
       </c>
       <c r="G55">
-        <v>5308</v>
+        <v>5332</v>
       </c>
       <c r="H55">
-        <v>11163</v>
+        <v>11215</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
       </c>
       <c r="D56">
-        <v>12.2</v>
+        <v>12.21</v>
       </c>
       <c r="E56">
-        <v>96402</v>
+        <v>96528</v>
       </c>
       <c r="F56">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="G56">
-        <v>3151</v>
+        <v>3155</v>
       </c>
       <c r="H56">
-        <v>7113</v>
+        <v>7122</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -6639,117 +6639,117 @@
         <v>11.97</v>
       </c>
       <c r="E57">
-        <v>939812</v>
+        <v>939717</v>
       </c>
       <c r="F57">
         <v>11.19</v>
       </c>
       <c r="G57">
-        <v>46394</v>
+        <v>46389</v>
       </c>
       <c r="H57">
-        <v>78718</v>
+        <v>78710</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
       </c>
       <c r="D58">
-        <v>8.68</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="E58">
-        <v>541294</v>
+        <v>542694</v>
       </c>
       <c r="F58">
-        <v>9.2899999999999991</v>
+        <v>9.31</v>
       </c>
       <c r="G58">
-        <v>45489</v>
+        <v>45606</v>
       </c>
       <c r="H58">
-        <v>41921</v>
+        <v>42030</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
       </c>
       <c r="D59">
-        <v>4.37</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="E59">
-        <v>303228</v>
+        <v>302521</v>
       </c>
       <c r="F59">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="G59">
-        <v>23530</v>
+        <v>23475</v>
       </c>
       <c r="H59">
-        <v>29587</v>
+        <v>29518</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
       </c>
       <c r="D60">
-        <v>12.18</v>
+        <v>12.26</v>
       </c>
       <c r="E60">
-        <v>454942</v>
+        <v>457808</v>
       </c>
       <c r="F60">
-        <v>13.64</v>
+        <v>13.72</v>
       </c>
       <c r="G60">
-        <v>17447</v>
+        <v>17557</v>
       </c>
       <c r="H60">
-        <v>32513</v>
+        <v>32718</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
       </c>
       <c r="D61">
-        <v>9.9600000000000009</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="E61">
-        <v>5238695</v>
+        <v>5244046</v>
       </c>
       <c r="F61">
-        <v>10.31</v>
+        <v>10.32</v>
       </c>
       <c r="G61">
-        <v>330386</v>
+        <v>330860</v>
       </c>
       <c r="H61">
-        <v>420769</v>
+        <v>421183</v>
       </c>
     </row>
   </sheetData>
@@ -6769,55 +6769,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -6840,10 +6840,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -6866,10 +6866,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -6918,10 +6918,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -6944,10 +6944,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -6970,10 +6970,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -6996,10 +6996,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -7022,10 +7022,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -7048,10 +7048,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -7074,10 +7074,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -7100,10 +7100,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -7126,10 +7126,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -7152,10 +7152,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -7178,10 +7178,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -7230,10 +7230,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -7256,10 +7256,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -7282,10 +7282,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -7308,10 +7308,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -7334,10 +7334,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -7438,10 +7438,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -7464,10 +7464,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -7490,10 +7490,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -7516,7 +7516,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -7565,10 +7565,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -7617,10 +7617,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -7643,10 +7643,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -7669,10 +7669,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -7695,10 +7695,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -7747,10 +7747,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -7773,10 +7773,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -7825,10 +7825,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -7903,10 +7903,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -7929,10 +7929,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -8007,10 +8007,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -8033,10 +8033,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -8085,10 +8085,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -8111,10 +8111,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -8137,7 +8137,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -8175,55 +8175,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -8246,10 +8246,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -8272,10 +8272,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -8298,10 +8298,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -8324,10 +8324,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -8350,10 +8350,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -8376,10 +8376,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -8402,10 +8402,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -8428,10 +8428,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -8480,10 +8480,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -8532,10 +8532,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -8558,10 +8558,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -8584,10 +8584,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -8610,10 +8610,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -8662,10 +8662,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -8688,10 +8688,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -8714,10 +8714,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -8740,10 +8740,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -8766,10 +8766,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -8792,10 +8792,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -8818,10 +8818,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -8844,10 +8844,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -8896,10 +8896,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -8922,7 +8922,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -8945,10 +8945,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -8971,10 +8971,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -8997,10 +8997,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -9023,10 +9023,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -9049,10 +9049,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -9075,10 +9075,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -9101,10 +9101,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -9127,10 +9127,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -9179,10 +9179,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -9205,10 +9205,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -9231,10 +9231,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -9257,10 +9257,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -9283,10 +9283,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -9309,10 +9309,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -9361,10 +9361,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -9387,10 +9387,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -9413,10 +9413,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -9439,10 +9439,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -9465,10 +9465,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -9491,10 +9491,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -9517,10 +9517,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -9543,7 +9543,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -9581,55 +9581,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -9652,10 +9652,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -9704,10 +9704,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -9730,10 +9730,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -9756,10 +9756,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -9782,10 +9782,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -9834,10 +9834,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -9912,10 +9912,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -9938,10 +9938,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -9964,10 +9964,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -9990,10 +9990,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -10016,10 +10016,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -10042,10 +10042,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -10068,10 +10068,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -10120,10 +10120,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -10146,10 +10146,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -10172,10 +10172,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -10198,10 +10198,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -10224,10 +10224,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -10250,10 +10250,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -10302,10 +10302,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -10351,10 +10351,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -10377,10 +10377,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -10403,10 +10403,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -10429,10 +10429,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -10455,10 +10455,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -10481,10 +10481,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -10585,10 +10585,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -10611,10 +10611,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -10637,10 +10637,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -10663,10 +10663,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -10689,10 +10689,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -10715,10 +10715,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -10767,10 +10767,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -10793,10 +10793,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -10819,10 +10819,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -10845,10 +10845,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -10871,10 +10871,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -10897,10 +10897,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -10923,10 +10923,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -10949,7 +10949,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -10987,55 +10987,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -11058,10 +11058,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -11084,10 +11084,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -11110,10 +11110,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -11136,10 +11136,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -11162,10 +11162,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -11188,10 +11188,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -11214,10 +11214,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -11240,10 +11240,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -11266,10 +11266,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -11292,10 +11292,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -11318,10 +11318,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -11344,10 +11344,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -11370,10 +11370,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -11396,10 +11396,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -11422,10 +11422,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -11448,10 +11448,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -11474,10 +11474,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -11500,10 +11500,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -11552,10 +11552,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -11578,10 +11578,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -11604,10 +11604,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -11630,10 +11630,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -11656,10 +11656,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -11682,10 +11682,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -11708,10 +11708,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -11734,7 +11734,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -11783,10 +11783,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -11809,10 +11809,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -11835,10 +11835,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -11861,10 +11861,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -11887,10 +11887,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -11913,10 +11913,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -11939,10 +11939,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -11965,10 +11965,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -11991,10 +11991,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -12017,10 +12017,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -12043,10 +12043,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -12069,10 +12069,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -12095,10 +12095,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -12121,10 +12121,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -12147,10 +12147,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -12173,10 +12173,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -12199,10 +12199,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -12225,10 +12225,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -12251,10 +12251,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -12277,10 +12277,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -12303,10 +12303,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -12329,10 +12329,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -12355,7 +12355,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -12393,55 +12393,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -12464,10 +12464,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -12490,10 +12490,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -12516,10 +12516,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -12542,10 +12542,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -12568,10 +12568,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -12594,10 +12594,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -12620,10 +12620,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -12646,10 +12646,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -12672,10 +12672,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -12698,10 +12698,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -12724,10 +12724,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -12750,10 +12750,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -12776,10 +12776,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -12802,10 +12802,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -12828,10 +12828,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -12854,10 +12854,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -12880,10 +12880,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -12906,10 +12906,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -12932,10 +12932,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -12958,10 +12958,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -12984,10 +12984,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -13010,10 +13010,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -13036,10 +13036,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -13062,10 +13062,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -13088,10 +13088,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -13140,7 +13140,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -13163,10 +13163,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -13189,10 +13189,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -13215,10 +13215,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -13241,10 +13241,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -13267,10 +13267,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -13293,10 +13293,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -13319,10 +13319,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -13345,10 +13345,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -13371,10 +13371,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -13397,10 +13397,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -13423,10 +13423,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -13449,10 +13449,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -13475,10 +13475,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -13501,10 +13501,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -13527,10 +13527,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -13553,10 +13553,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -13579,10 +13579,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -13605,10 +13605,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -13631,10 +13631,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -13657,10 +13657,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -13683,10 +13683,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -13709,10 +13709,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -13735,10 +13735,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -13799,55 +13799,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -13870,10 +13870,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -13896,10 +13896,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -13922,10 +13922,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -13948,10 +13948,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -13974,10 +13974,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -14000,10 +14000,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -14026,10 +14026,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -14052,10 +14052,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -14078,10 +14078,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -14104,10 +14104,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -14130,10 +14130,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -14156,10 +14156,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -14182,10 +14182,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -14208,10 +14208,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -14234,10 +14234,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -14260,10 +14260,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -14286,10 +14286,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -14312,10 +14312,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -14338,10 +14338,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -14364,10 +14364,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -14390,10 +14390,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -14416,10 +14416,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -14442,10 +14442,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -14468,10 +14468,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -14494,10 +14494,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -14520,10 +14520,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -14546,7 +14546,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -14569,10 +14569,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -14595,10 +14595,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -14621,10 +14621,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -14647,10 +14647,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -14673,10 +14673,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -14699,10 +14699,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -14725,10 +14725,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -14751,10 +14751,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -14777,10 +14777,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -14803,10 +14803,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -14829,10 +14829,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -14855,10 +14855,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -14881,10 +14881,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -14907,10 +14907,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -14933,10 +14933,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -14959,10 +14959,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -14985,10 +14985,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -15011,10 +15011,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -15037,10 +15037,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -15063,10 +15063,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -15089,10 +15089,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -15115,10 +15115,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -15141,10 +15141,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -15167,7 +15167,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -15205,55 +15205,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -15276,10 +15276,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -15302,10 +15302,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -15328,10 +15328,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -15354,10 +15354,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -15380,10 +15380,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -15406,10 +15406,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -15432,10 +15432,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -15458,10 +15458,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -15484,10 +15484,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -15510,10 +15510,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -15536,10 +15536,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -15562,10 +15562,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -15588,10 +15588,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -15614,10 +15614,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -15640,10 +15640,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -15666,10 +15666,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -15692,10 +15692,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -15718,10 +15718,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -15744,10 +15744,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -15770,10 +15770,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -15796,10 +15796,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -15822,10 +15822,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -15848,10 +15848,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -15874,10 +15874,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -15900,10 +15900,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -15926,10 +15926,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -15952,7 +15952,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -15975,10 +15975,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -16001,10 +16001,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -16027,10 +16027,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -16053,10 +16053,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -16079,10 +16079,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -16105,10 +16105,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -16131,10 +16131,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -16157,10 +16157,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -16183,10 +16183,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -16209,10 +16209,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -16235,10 +16235,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -16261,10 +16261,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -16287,10 +16287,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -16313,10 +16313,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -16339,10 +16339,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -16365,10 +16365,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -16391,10 +16391,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -16417,10 +16417,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -16443,10 +16443,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -16469,10 +16469,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -16495,10 +16495,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -16521,10 +16521,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -16547,10 +16547,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -16573,7 +16573,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>
@@ -16611,55 +16611,55 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>10</v>
-      </c>
-      <c r="H9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
       </c>
       <c r="C10">
         <v>8.93</v>
@@ -16682,10 +16682,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>11.89</v>
@@ -16708,10 +16708,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>5.91</v>
@@ -16734,10 +16734,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>3.49</v>
@@ -16760,10 +16760,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>1.49</v>
@@ -16786,10 +16786,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>10.11</v>
@@ -16812,10 +16812,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>6.13</v>
@@ -16838,10 +16838,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1.24</v>
@@ -16864,10 +16864,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>5.48</v>
@@ -16890,10 +16890,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19">
         <v>67.94</v>
@@ -16916,10 +16916,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>80.55</v>
@@ -16942,10 +16942,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>9.2799999999999994</v>
@@ -16968,10 +16968,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22">
         <v>9.07</v>
@@ -16994,10 +16994,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23">
         <v>5.82</v>
@@ -17020,10 +17020,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24">
         <v>55.22</v>
@@ -17046,10 +17046,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1.64</v>
@@ -17072,10 +17072,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>2.48</v>
@@ -17098,10 +17098,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0.76</v>
@@ -17124,10 +17124,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28">
         <v>0.55000000000000004</v>
@@ -17150,10 +17150,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>19.059999999999999</v>
@@ -17176,10 +17176,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30">
         <v>35.18</v>
@@ -17202,10 +17202,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31">
         <v>10.08</v>
@@ -17228,10 +17228,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32">
         <v>17.21</v>
@@ -17254,10 +17254,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C33">
         <v>5.19</v>
@@ -17280,10 +17280,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>2.0499999999999998</v>
@@ -17306,10 +17306,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>46.59</v>
@@ -17332,10 +17332,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>11.08</v>
@@ -17358,7 +17358,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37">
         <v>434.42</v>
@@ -17381,10 +17381,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
       </c>
       <c r="C38">
         <v>2.46</v>
@@ -17407,10 +17407,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39">
         <v>2.67</v>
@@ -17433,10 +17433,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>11.08</v>
@@ -17459,10 +17459,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41">
         <v>8.06</v>
@@ -17485,10 +17485,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42">
         <v>2.75</v>
@@ -17511,10 +17511,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43">
         <v>3.73</v>
@@ -17537,10 +17537,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>0.43</v>
@@ -17563,10 +17563,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>24.25</v>
@@ -17589,10 +17589,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1.67</v>
@@ -17615,10 +17615,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>8.76</v>
@@ -17641,10 +17641,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1.64</v>
@@ -17667,10 +17667,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>2.57</v>
@@ -17693,10 +17693,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>0.56999999999999995</v>
@@ -17719,10 +17719,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>5.85</v>
@@ -17745,10 +17745,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>101.7</v>
@@ -17771,10 +17771,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53">
         <v>5.99</v>
@@ -17797,10 +17797,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54">
         <v>9.2799999999999994</v>
@@ -17823,10 +17823,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C55">
         <v>13.71</v>
@@ -17849,10 +17849,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56">
         <v>8.93</v>
@@ -17875,10 +17875,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>91.01</v>
@@ -17901,10 +17901,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58">
         <v>35.270000000000003</v>
@@ -17927,10 +17927,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59">
         <v>73.78</v>
@@ -17953,10 +17953,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60">
         <v>46.04</v>
@@ -17979,7 +17979,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61">
         <v>462.21</v>

--- a/Raw_Data/v7a_2040_yoll_Europe.xlsx
+++ b/Raw_Data/v7a_2040_yoll_Europe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\StefanÅström\C_Verktyg\Python\ALL_PYTHON\2026_v7_Goth_Prot_CBA\Raw_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2873D7D7-328E-4B1F-8409-8FC26B31F562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780B4C70-9248-49B4-832D-0ADF567BF472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FF85C77-6106-4259-AF19-728A5860A454}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="9" xr2:uid="{0FF85C77-6106-4259-AF19-728A5860A454}"/>
   </bookViews>
   <sheets>
     <sheet name="yoll_Europe (13)" sheetId="12" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="78">
   <si>
     <t>Premature mortality due to PM2.5</t>
   </si>
@@ -276,11 +276,18 @@
   <si>
     <t>Scenario: Baseline_v7a</t>
   </si>
+  <si>
+    <t>Delta</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -714,7 +721,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -757,11 +764,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -789,6 +799,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
     <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
@@ -2541,7 +2552,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D4EB34D-BB41-4D94-B9C0-449A8C9FC5EE}">
-  <dimension ref="A2:H61"/>
+  <dimension ref="A2:H66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -3938,6 +3949,21 @@
       </c>
       <c r="H61">
         <v>363206</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H64" s="1">
+        <f>H61+H37</f>
+        <v>589623</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G66" t="s">
+        <v>77</v>
+      </c>
+      <c r="H66" s="2">
+        <f>yoll_Europe!H64-'yoll_Europe (4)'!H64</f>
+        <v>69386</v>
       </c>
     </row>
   </sheetData>
@@ -5353,8 +5379,12 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{231A728B-B86D-46F2-B241-D89DAD486E32}">
-  <dimension ref="A2:H61"/>
+  <dimension ref="A2:H64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -6750,6 +6780,16 @@
       </c>
       <c r="H61">
         <v>421183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E64" s="1">
+        <f>E61+E37</f>
+        <v>7594303</v>
+      </c>
+      <c r="H64" s="1">
+        <f>H61+H37</f>
+        <v>659009</v>
       </c>
     </row>
   </sheetData>
